--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -38,6 +38,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="투표결과" sheetId="29" state="visible" r:id="rId29"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="엔딩" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="획득" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작품테스터" sheetId="32" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -729,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="37" min="1" max="1"/>
@@ -814,7 +815,7 @@
         </is>
       </c>
       <c r="C7" s="42" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="44" t="n"/>
     </row>
@@ -1195,6 +1196,20 @@
         <v>10</v>
       </c>
       <c r="D34" s="44" t="n"/>
+    </row>
+    <row r="35" ht="16.5" customHeight="1" s="38">
+      <c r="A35" s="42" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="43" t="inlineStr">
+        <is>
+          <t>작품테스터</t>
+        </is>
+      </c>
+      <c r="C35" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" s="44" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1227,6 +1242,7 @@
     <hyperlink ref="B32" location="'투표결과'!A1" display="투표결과"/>
     <hyperlink ref="B33" location="'엔딩'!A1" display="엔딩"/>
     <hyperlink ref="B34" location="'획득'!A1" display="획득"/>
+    <hyperlink ref="B35" location="'작품테스터'!A1" display="작품테스터"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9972,13 +9988,330 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.62109375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="14" customWidth="1" style="37" min="1" max="1"/>
+    <col width="24" customWidth="1" style="37" min="2" max="2"/>
+    <col width="40" customWidth="1" style="37" min="3" max="3"/>
+    <col width="16" customWidth="1" style="37" min="4" max="4"/>
+    <col width="12" customWidth="1" style="37" min="5" max="5"/>
+    <col width="18.62" customWidth="1" style="37" min="6" max="6"/>
+    <col width="40" customWidth="1" style="37" min="7" max="7"/>
+    <col width="57.02" customWidth="1" style="37" min="8" max="8"/>
+    <col width="8.619999999999999" customWidth="1" style="37" min="9" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.5" customHeight="1" s="38">
+      <c r="A1" s="45" t="inlineStr">
+        <is>
+          <t>테이블명</t>
+        </is>
+      </c>
+      <c r="B1" s="46" t="inlineStr">
+        <is>
+          <t>작품테스터</t>
+        </is>
+      </c>
+      <c r="C1" s="47" t="n"/>
+      <c r="D1" s="47" t="n"/>
+      <c r="E1" s="47" t="n"/>
+      <c r="F1" s="47" t="n"/>
+      <c r="G1" s="47" t="n"/>
+      <c r="H1" s="48" t="n"/>
+      <c r="J1" s="49" t="inlineStr">
+        <is>
+          <t>← 목차</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1" s="38">
+      <c r="A2" s="45" t="inlineStr">
+        <is>
+          <t>테이블 설명</t>
+        </is>
+      </c>
+      <c r="B2" s="44" t="inlineStr">
+        <is>
+          <t>작품별 테스트 플레이 권한 테이블</t>
+        </is>
+      </c>
+      <c r="C2" s="47" t="n"/>
+      <c r="D2" s="47" t="n"/>
+      <c r="E2" s="47" t="n"/>
+      <c r="F2" s="47" t="n"/>
+      <c r="G2" s="47" t="n"/>
+      <c r="H2" s="48" t="n"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="38">
+      <c r="A4" s="41" t="inlineStr">
+        <is>
+          <t>순번</t>
+        </is>
+      </c>
+      <c r="B4" s="41" t="inlineStr">
+        <is>
+          <t>컬럼명</t>
+        </is>
+      </c>
+      <c r="C4" s="41" t="inlineStr">
+        <is>
+          <t>컬럼 설명</t>
+        </is>
+      </c>
+      <c r="D4" s="41" t="inlineStr">
+        <is>
+          <t>데이터타입</t>
+        </is>
+      </c>
+      <c r="E4" s="41" t="inlineStr">
+        <is>
+          <t>Null허용</t>
+        </is>
+      </c>
+      <c r="F4" s="41" t="inlineStr">
+        <is>
+          <t>기본값</t>
+        </is>
+      </c>
+      <c r="G4" s="41" t="inlineStr">
+        <is>
+          <t>특징</t>
+        </is>
+      </c>
+      <c r="H4" s="41" t="inlineStr">
+        <is>
+          <t>제약조건</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="38">
+      <c r="A5" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="50" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>작품 테스터 식별 번호</t>
+        </is>
+      </c>
+      <c r="D5" s="64" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E5" s="64" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F5" s="64" t="inlineStr">
+        <is>
+          <t>자동생성</t>
+        </is>
+      </c>
+      <c r="G5" s="64" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="H5" s="64" t="inlineStr">
+        <is>
+          <t>기본키(PK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="38">
+      <c r="A6" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="50" t="inlineStr">
+        <is>
+          <t>작품_번호</t>
+        </is>
+      </c>
+      <c r="C6" s="55" t="inlineStr">
+        <is>
+          <t>테스트 대상 작품 식별 번호</t>
+        </is>
+      </c>
+      <c r="D6" s="64" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E6" s="64" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F6" s="64" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G6" s="64" t="inlineStr">
+        <is>
+          <t>제작자는 자기 작품에, 관리자·운영자는 모든 작품에 테스터를 지정할 수 있음</t>
+        </is>
+      </c>
+      <c r="H6" s="64" t="inlineStr">
+        <is>
+          <t>외래키(FK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="38">
+      <c r="A7" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="50" t="inlineStr">
+        <is>
+          <t>계정_번호</t>
+        </is>
+      </c>
+      <c r="C7" s="55" t="inlineStr">
+        <is>
+          <t>테스터 권한을 받은 계정 식별 번호</t>
+        </is>
+      </c>
+      <c r="D7" s="64" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E7" s="64" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F7" s="64" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G7" s="64" t="inlineStr">
+        <is>
+          <t>한 작품에 계정별 한 번만 부여</t>
+        </is>
+      </c>
+      <c r="H7" s="64" t="inlineStr">
+        <is>
+          <t>외래키(FK), 복합 UNIQUE(작품_번호, 계정_번호)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="38">
+      <c r="A8" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="50" t="inlineStr">
+        <is>
+          <t>부여일시</t>
+        </is>
+      </c>
+      <c r="C8" s="55" t="inlineStr">
+        <is>
+          <t>테스터 권한 부여 일시</t>
+        </is>
+      </c>
+      <c r="D8" s="64" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="E8" s="64" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F8" s="64" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G8" s="64" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H8" s="64" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="38">
+      <c r="A9" s="42" t="n"/>
+      <c r="B9" s="50" t="n"/>
+      <c r="C9" s="55" t="n"/>
+      <c r="D9" s="64" t="n"/>
+      <c r="E9" s="55" t="n"/>
+      <c r="F9" s="55" t="n"/>
+      <c r="G9" s="55" t="n"/>
+      <c r="H9" s="55" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="38">
+      <c r="A10" s="42" t="n"/>
+      <c r="B10" s="50" t="n"/>
+      <c r="C10" s="55" t="n"/>
+      <c r="D10" s="55" t="n"/>
+      <c r="E10" s="55" t="n"/>
+      <c r="F10" s="55" t="n"/>
+      <c r="G10" s="55" t="n"/>
+      <c r="H10" s="55" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="38">
+      <c r="A11" s="42" t="n"/>
+      <c r="B11" s="50" t="n"/>
+      <c r="C11" s="55" t="n"/>
+      <c r="D11" s="72" t="n"/>
+      <c r="E11" s="55" t="n"/>
+      <c r="F11" s="55" t="n"/>
+      <c r="G11" s="55" t="n"/>
+      <c r="H11" s="55" t="n"/>
+    </row>
+    <row r="12" ht="16.5" customHeight="1" s="38">
+      <c r="A12" s="56" t="n"/>
+      <c r="B12" s="56" t="n"/>
+      <c r="C12" s="56" t="n"/>
+      <c r="D12" s="56" t="n"/>
+      <c r="E12" s="56" t="n"/>
+      <c r="F12" s="56" t="n"/>
+      <c r="G12" s="56" t="n"/>
+      <c r="H12" s="56" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="J1" location="'목차'!A1" display="← 목차"/>
+  </hyperlinks>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="37" min="1" max="1"/>
@@ -10514,6 +10847,46 @@
       </c>
       <c r="G17" s="44" t="n"/>
       <c r="H17" s="44" t="n"/>
+    </row>
+    <row r="18" ht="16.5" customHeight="1" s="38">
+      <c r="A18" s="42" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="50" t="inlineStr">
+        <is>
+          <t>공개권한</t>
+        </is>
+      </c>
+      <c r="C18" s="44" t="inlineStr">
+        <is>
+          <t>비공개 상태에서 다시 공개할 수 있는 주체</t>
+        </is>
+      </c>
+      <c r="D18" s="44" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="E18" s="44" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F18" s="53" t="inlineStr">
+        <is>
+          <t>'제작자'</t>
+        </is>
+      </c>
+      <c r="G18" s="44" t="inlineStr">
+        <is>
+          <t>'제작자', '관리자', '운영자' 중 하나 (제작자가 비공개하면 제작자만, 관리자가 비공개하면 관리자 이상, 운영자가 비공개하면 운영자만 공개 가능)</t>
+        </is>
+      </c>
+      <c r="H18" s="44" t="inlineStr">
+        <is>
+          <t>CHECK (공개권한 IN ('제작자', '관리자', '운영자'))</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="C27" s="42" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D27" s="44" t="n"/>
     </row>
@@ -6570,7 +6570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.62109375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="37" min="1" max="1"/>
@@ -6924,6 +6924,86 @@
       <c r="H11" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16.5" customHeight="1" s="38">
+      <c r="A12" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="50" t="inlineStr">
+        <is>
+          <t>작품_번호</t>
+        </is>
+      </c>
+      <c r="C12" s="44" t="inlineStr">
+        <is>
+          <t>방에서 진행할 작품 식별 번호</t>
+        </is>
+      </c>
+      <c r="D12" s="60" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E12" s="44" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F12" s="44" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G12" s="44" t="inlineStr">
+        <is>
+          <t>방 생성 시 선택. 1방 1게임</t>
+        </is>
+      </c>
+      <c r="H12" s="44" t="inlineStr">
+        <is>
+          <t>외래키(FK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16.5" customHeight="1" s="38">
+      <c r="A13" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="50" t="inlineStr">
+        <is>
+          <t>버전_버전</t>
+        </is>
+      </c>
+      <c r="C13" s="44" t="inlineStr">
+        <is>
+          <t>방에서 진행할 작품 버전</t>
+        </is>
+      </c>
+      <c r="D13" s="60" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="E13" s="44" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F13" s="44" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G13" s="44" t="inlineStr">
+        <is>
+          <t>방 생성 시 해당 작품의 확정된 최신 버전이 자동으로 정해짐</t>
+        </is>
+      </c>
+      <c r="H13" s="44" t="inlineStr">
+        <is>
+          <t>복합 외래키(작품_번호, 버전_버전), 복합 UNIQUE(번호, 작품_번호, 버전_버전)</t>
         </is>
       </c>
     </row>
@@ -6992,7 +7072,7 @@
       </c>
       <c r="B2" s="65" t="inlineStr">
         <is>
-          <t>방에서 플레이하는 작품 하나의 버전과 현재 진행 상태를 기록</t>
+          <t>방에서 플레이하는 작품 하나의 버전과 현재 진행 상태를 기록 (1방 1게임)</t>
         </is>
       </c>
       <c r="C2" s="47" t="n"/>
@@ -7002,6 +7082,7 @@
       <c r="G2" s="47" t="n"/>
       <c r="H2" s="48" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="16.5" customHeight="1" s="38">
       <c r="A4" s="41" t="inlineStr">
         <is>
@@ -7113,10 +7194,14 @@
           <t>없음</t>
         </is>
       </c>
-      <c r="G6" s="60" t="n"/>
+      <c r="G6" s="60" t="inlineStr">
+        <is>
+          <t>한 방에 게임은 하나</t>
+        </is>
+      </c>
       <c r="H6" s="60" t="inlineStr">
         <is>
-          <t>외래키(FK)</t>
+          <t>외래키(FK), UNIQUE</t>
         </is>
       </c>
     </row>
@@ -7188,7 +7273,7 @@
       <c r="G8" s="60" t="n"/>
       <c r="H8" s="60" t="inlineStr">
         <is>
-          <t>복합 외래키(작품_번호, 버전_버전)</t>
+          <t>복합 외래키(작품_번호, 버전_버전), 복합 외래키(방_번호, 작품_번호, 버전_버전)</t>
         </is>
       </c>
     </row>

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -38,7 +38,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="투표결과" sheetId="29" state="visible" r:id="rId29"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="엔딩" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="획득" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작품테스터" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="테스터" sheetId="32" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B35" s="43" t="inlineStr">
         <is>
-          <t>작품테스터</t>
+          <t>테스터</t>
         </is>
       </c>
       <c r="C35" s="42" t="n">
@@ -1242,7 +1242,7 @@
     <hyperlink ref="B32" location="'투표결과'!A1" display="투표결과"/>
     <hyperlink ref="B33" location="'엔딩'!A1" display="엔딩"/>
     <hyperlink ref="B34" location="'획득'!A1" display="획득"/>
-    <hyperlink ref="B35" location="'작품테스터'!A1" display="작품테스터"/>
+    <hyperlink ref="B35" location="'테스터'!A1" display="테스터"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7082,7 +7082,6 @@
       <c r="G2" s="47" t="n"/>
       <c r="H2" s="48" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4" ht="16.5" customHeight="1" s="38">
       <c r="A4" s="41" t="inlineStr">
         <is>
@@ -10101,7 +10100,7 @@
       </c>
       <c r="B1" s="46" t="inlineStr">
         <is>
-          <t>작품테스터</t>
+          <t>테스터</t>
         </is>
       </c>
       <c r="C1" s="47" t="n"/>

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -754,7 +754,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16.5" customHeight="1" s="38">
       <c r="A4" s="41" t="inlineStr">
         <is>
@@ -1067,7 +1066,7 @@
         </is>
       </c>
       <c r="C25" s="42" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D25" s="44" t="n"/>
     </row>
@@ -1081,7 +1080,7 @@
         </is>
       </c>
       <c r="C26" s="42" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D26" s="44" t="n"/>
     </row>
@@ -5949,7 +5948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.62109375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="37" min="1" max="1"/>
@@ -5994,7 +5993,7 @@
       </c>
       <c r="B2" s="44" t="inlineStr">
         <is>
-          <t>공통 또는 제작자별로 사용하는 진행 단계와 기본 규칙</t>
+          <t>공통 또는 제작자별로 사용하는 진행 단계와 기본 규칙. 내용은 수정하지 않고 같은 이름으로 버전을 올려 새 행을 추가한다. 삭제는 삭제일시 표시로 한다. 계정_번호가 비어 있으면 공통(시스템 제공) 항목</t>
         </is>
       </c>
       <c r="C2" s="47" t="n"/>
@@ -6116,7 +6115,11 @@
         </is>
       </c>
       <c r="G6" s="44" t="n"/>
-      <c r="H6" s="44" t="n"/>
+      <c r="H6" s="44" t="inlineStr">
+        <is>
+          <t>복합 UNIQUE(계정_번호, 이름, 버전)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="16.5" customHeight="1" s="38">
       <c r="A7" s="42" t="n">
@@ -6218,9 +6221,119 @@
       <c r="G9" s="44" t="n"/>
       <c r="H9" s="44" t="inlineStr">
         <is>
-          <t>외래키(FK)</t>
-        </is>
-      </c>
+          <t>외래키(FK), 복합 UNIQUE(계정_번호, 이름, 버전)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="38">
+      <c r="A10" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="50" t="inlineStr">
+        <is>
+          <t>버전</t>
+        </is>
+      </c>
+      <c r="C10" s="44" t="inlineStr">
+        <is>
+          <t>같은 계정·이름 안에서의 버전 번호</t>
+        </is>
+      </c>
+      <c r="D10" s="51" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E10" s="44" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F10" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="44" t="inlineStr">
+        <is>
+          <t>계열(계정_번호+이름) 안의 순번. 수정은 버전을 올린 새 행으로 한다</t>
+        </is>
+      </c>
+      <c r="H10" s="44" t="inlineStr">
+        <is>
+          <t>복합 UNIQUE(계정_번호, 이름, 버전), CHECK (버전 &gt;= 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="38">
+      <c r="A11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="50" t="inlineStr">
+        <is>
+          <t>변경내역</t>
+        </is>
+      </c>
+      <c r="C11" s="44" t="inlineStr">
+        <is>
+          <t>이 버전에서 바뀐 내용</t>
+        </is>
+      </c>
+      <c r="D11" s="51" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="E11" s="44" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F11" s="44" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G11" s="44" t="inlineStr">
+        <is>
+          <t>제작자가 항목을 고를 때 보여 준다</t>
+        </is>
+      </c>
+      <c r="H11" s="44" t="n"/>
+    </row>
+    <row r="12" ht="16.5" customHeight="1" s="38">
+      <c r="A12" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="50" t="inlineStr">
+        <is>
+          <t>삭제일시</t>
+        </is>
+      </c>
+      <c r="C12" s="44" t="inlineStr">
+        <is>
+          <t>삭제 표시한 일시</t>
+        </is>
+      </c>
+      <c r="D12" s="51" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="E12" s="44" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F12" s="44" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G12" s="44" t="inlineStr">
+        <is>
+          <t>값이 있으면 삭제된 항목(새로 선택 불가). 행·확정 스냅샷은 남는다. 한 번 표시하면 되돌릴 수 없다</t>
+        </is>
+      </c>
+      <c r="H12" s="44" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6242,7 +6355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.62109375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="56" min="1" max="1"/>
@@ -6286,7 +6399,7 @@
       </c>
       <c r="B2" s="44" t="inlineStr">
         <is>
-          <t>다양한 새로운 기믹을 저장하는 테이블</t>
+          <t>다양한 새로운 기믹을 저장하는 테이블. 내용은 수정하지 않고 같은 이름으로 버전을 올려 새 행을 추가한다. 삭제는 삭제일시 표시로 한다. 계정_번호가 비어 있으면 공통(시스템 제공) 항목</t>
         </is>
       </c>
       <c r="C2" s="47" t="n"/>
@@ -6410,7 +6523,7 @@
       <c r="G6" s="63" t="n"/>
       <c r="H6" s="69" t="inlineStr">
         <is>
-          <t>외래키(FK)</t>
+          <t>외래키(FK), 복합 UNIQUE(계정_번호, 이름, 버전)</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6557,11 @@
         </is>
       </c>
       <c r="G7" s="63" t="n"/>
-      <c r="H7" s="63" t="n"/>
+      <c r="H7" s="63" t="inlineStr">
+        <is>
+          <t>복합 UNIQUE(계정_번호, 이름, 버전)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" s="38">
       <c r="A8" s="42" t="n">
@@ -6549,6 +6666,116 @@
         </is>
       </c>
       <c r="H10" s="63" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="38">
+      <c r="A11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="59" t="inlineStr">
+        <is>
+          <t>버전</t>
+        </is>
+      </c>
+      <c r="C11" s="63" t="inlineStr">
+        <is>
+          <t>같은 계정·이름 안에서의 버전 번호</t>
+        </is>
+      </c>
+      <c r="D11" s="63" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E11" s="63" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F11" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="60" t="inlineStr">
+        <is>
+          <t>계열(계정_번호+이름) 안의 순번. 수정은 버전을 올린 새 행으로 한다</t>
+        </is>
+      </c>
+      <c r="H11" s="63" t="inlineStr">
+        <is>
+          <t>복합 UNIQUE(계정_번호, 이름, 버전), CHECK (버전 &gt;= 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16.5" customHeight="1" s="38">
+      <c r="A12" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="59" t="inlineStr">
+        <is>
+          <t>변경내역</t>
+        </is>
+      </c>
+      <c r="C12" s="63" t="inlineStr">
+        <is>
+          <t>이 버전에서 바뀐 내용</t>
+        </is>
+      </c>
+      <c r="D12" s="63" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="E12" s="63" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F12" s="63" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G12" s="60" t="inlineStr">
+        <is>
+          <t>제작자가 항목을 고를 때 보여 준다</t>
+        </is>
+      </c>
+      <c r="H12" s="63" t="n"/>
+    </row>
+    <row r="13" ht="16.5" customHeight="1" s="38">
+      <c r="A13" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="59" t="inlineStr">
+        <is>
+          <t>삭제일시</t>
+        </is>
+      </c>
+      <c r="C13" s="63" t="inlineStr">
+        <is>
+          <t>삭제 표시한 일시</t>
+        </is>
+      </c>
+      <c r="D13" s="63" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="E13" s="63" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F13" s="63" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G13" s="60" t="inlineStr">
+        <is>
+          <t>값이 있으면 삭제된 항목(새로 선택 불가). 행·확정 스냅샷은 남는다. 한 번 표시하면 되돌릴 수 없다</t>
+        </is>
+      </c>
+      <c r="H13" s="63" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="C25" s="42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="44" t="n"/>
     </row>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="C26" s="42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="44" t="n"/>
     </row>
@@ -5948,7 +5948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.62109375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="37" min="1" max="1"/>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="B2" s="44" t="inlineStr">
         <is>
-          <t>공통 또는 제작자별로 사용하는 진행 단계와 기본 규칙. 내용은 수정하지 않고 같은 이름으로 버전을 올려 새 행을 추가한다. 삭제는 삭제일시 표시로 한다. 계정_번호가 비어 있으면 공통(시스템 제공) 항목</t>
+          <t>공통 또는 제작자별로 사용하는 진행 단계와 기본 규칙. 내용은 수정하지 않고 같은 이름으로 버전을 올려 새 행을 추가한다. 삭제는 삭제일시 표시로 한다. 계정_번호가 비어 있으면 공통(시스템 제공) 항목. 공개여부는 다른 제작자와 공유할지를 나타낸다(공유 기능 전까지 쓰이지 않음)</t>
         </is>
       </c>
       <c r="C2" s="47" t="n"/>
@@ -6334,6 +6334,42 @@
         </is>
       </c>
       <c r="H12" s="44" t="n"/>
+    </row>
+    <row r="13" ht="16.5" customHeight="1" s="38">
+      <c r="A13" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="50" t="inlineStr">
+        <is>
+          <t>공개여부</t>
+        </is>
+      </c>
+      <c r="C13" s="44" t="inlineStr">
+        <is>
+          <t>다른 제작자에게 공유할지 여부</t>
+        </is>
+      </c>
+      <c r="D13" s="51" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="E13" s="44" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F13" s="44" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G13" s="44" t="inlineStr">
+        <is>
+          <t>공유 기능을 만들 때 쓴다(지금은 쓰이지 않음). 계정_번호가 비어 있는 공통 항목은 이 값과 무관하게 모두에게 보인다. 켜고 끌 수 있다</t>
+        </is>
+      </c>
+      <c r="H13" s="44" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6355,7 +6391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.62109375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="56" min="1" max="1"/>
@@ -6399,7 +6435,7 @@
       </c>
       <c r="B2" s="44" t="inlineStr">
         <is>
-          <t>다양한 새로운 기믹을 저장하는 테이블. 내용은 수정하지 않고 같은 이름으로 버전을 올려 새 행을 추가한다. 삭제는 삭제일시 표시로 한다. 계정_번호가 비어 있으면 공통(시스템 제공) 항목</t>
+          <t>다양한 새로운 기믹을 저장하는 테이블. 내용은 수정하지 않고 같은 이름으로 버전을 올려 새 행을 추가한다. 삭제는 삭제일시 표시로 한다. 계정_번호가 비어 있으면 공통(시스템 제공) 항목. 공개여부는 다른 제작자와 공유할지를 나타낸다(공유 기능 전까지 쓰이지 않음)</t>
         </is>
       </c>
       <c r="C2" s="47" t="n"/>
@@ -6776,6 +6812,42 @@
         </is>
       </c>
       <c r="H13" s="63" t="n"/>
+    </row>
+    <row r="14" ht="16.5" customHeight="1" s="38">
+      <c r="A14" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="59" t="inlineStr">
+        <is>
+          <t>공개여부</t>
+        </is>
+      </c>
+      <c r="C14" s="63" t="inlineStr">
+        <is>
+          <t>다른 제작자에게 공유할지 여부</t>
+        </is>
+      </c>
+      <c r="D14" s="63" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="E14" s="63" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F14" s="63" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G14" s="60" t="inlineStr">
+        <is>
+          <t>공유 기능을 만들 때 쓴다(지금은 쓰이지 않음). 계정_번호가 비어 있는 공통 항목은 이 값과 무관하게 모두에게 보인다. 켜고 끌 수 있다</t>
+        </is>
+      </c>
+      <c r="H14" s="63" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="C7" s="42" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" s="44" t="n"/>
     </row>
@@ -10694,7 +10694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="37" min="1" max="1"/>
@@ -11270,6 +11270,42 @@
           <t>CHECK (공개권한 IN ('제작자', '관리자', '운영자'))</t>
         </is>
       </c>
+    </row>
+    <row r="19" ht="16.5" customHeight="1" s="38">
+      <c r="A19" s="42" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="50" t="inlineStr">
+        <is>
+          <t>공통스토리</t>
+        </is>
+      </c>
+      <c r="C19" s="44" t="inlineStr">
+        <is>
+          <t>게임 시작 때 모든 플레이어가 읽는 공통 스토리(프롤로그)</t>
+        </is>
+      </c>
+      <c r="D19" s="44" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="E19" s="44" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F19" s="53" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G19" s="44" t="inlineStr">
+        <is>
+          <t>플레이 중 언제든 탭으로 다시 읽을 수 있다(보일 탭은 플레이 화면 설정에서 정함). 개인 서사는 인물.서사. 기믹으로 더 추가할 수 있다</t>
+        </is>
+      </c>
+      <c r="H19" s="44" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -39,6 +39,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="엔딩" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="획득" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="테스터" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자료" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -730,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="37" min="1" max="1"/>
@@ -1209,6 +1210,20 @@
         <v>4</v>
       </c>
       <c r="D35" s="44" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="42" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="43" t="inlineStr">
+        <is>
+          <t>자료</t>
+        </is>
+      </c>
+      <c r="C36" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="44" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1242,6 +1257,7 @@
     <hyperlink ref="B33" location="'엔딩'!A1" display="엔딩"/>
     <hyperlink ref="B34" location="'획득'!A1" display="획득"/>
     <hyperlink ref="B35" location="'테스터'!A1" display="테스터"/>
+    <hyperlink ref="B36" location="'자료'!A1" display="자료"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10688,6 +10704,307 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.62109375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="14" customWidth="1" style="37" min="1" max="1"/>
+    <col width="24" customWidth="1" style="37" min="2" max="2"/>
+    <col width="40" customWidth="1" style="37" min="3" max="3"/>
+    <col width="16" customWidth="1" style="37" min="4" max="4"/>
+    <col width="12" customWidth="1" style="37" min="5" max="5"/>
+    <col width="14" customWidth="1" style="37" min="6" max="6"/>
+    <col width="40" customWidth="1" style="37" min="7" max="7"/>
+    <col width="48.99" customWidth="1" style="37" min="8" max="8"/>
+    <col width="8.619999999999999" customWidth="1" style="37" min="9" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.5" customHeight="1" s="38">
+      <c r="A1" s="45" t="inlineStr">
+        <is>
+          <t>테이블명</t>
+        </is>
+      </c>
+      <c r="B1" s="46" t="inlineStr">
+        <is>
+          <t>자료</t>
+        </is>
+      </c>
+      <c r="C1" s="47" t="n"/>
+      <c r="D1" s="47" t="n"/>
+      <c r="E1" s="47" t="n"/>
+      <c r="F1" s="47" t="n"/>
+      <c r="G1" s="47" t="n"/>
+      <c r="H1" s="48" t="n"/>
+      <c r="J1" s="49" t="inlineStr">
+        <is>
+          <t>← 목차</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1" s="38">
+      <c r="A2" s="45" t="inlineStr">
+        <is>
+          <t>테이블 설명</t>
+        </is>
+      </c>
+      <c r="B2" s="44" t="inlineStr">
+        <is>
+          <t>기믹이 불러 쓰는 글을 작품 안에 따로 저장하는 테이블. 공통 스토리는 작품.공통스토리, 개인 서사는 인물.서사에 있다</t>
+        </is>
+      </c>
+      <c r="C2" s="47" t="n"/>
+      <c r="D2" s="47" t="n"/>
+      <c r="E2" s="47" t="n"/>
+      <c r="F2" s="47" t="n"/>
+      <c r="G2" s="47" t="n"/>
+      <c r="H2" s="48" t="n"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="38">
+      <c r="A4" s="41" t="inlineStr">
+        <is>
+          <t>순번</t>
+        </is>
+      </c>
+      <c r="B4" s="41" t="inlineStr">
+        <is>
+          <t>컬럼명</t>
+        </is>
+      </c>
+      <c r="C4" s="41" t="inlineStr">
+        <is>
+          <t>컬럼 설명</t>
+        </is>
+      </c>
+      <c r="D4" s="41" t="inlineStr">
+        <is>
+          <t>데이터타입</t>
+        </is>
+      </c>
+      <c r="E4" s="41" t="inlineStr">
+        <is>
+          <t>Null허용</t>
+        </is>
+      </c>
+      <c r="F4" s="41" t="inlineStr">
+        <is>
+          <t>기본값</t>
+        </is>
+      </c>
+      <c r="G4" s="41" t="inlineStr">
+        <is>
+          <t>특징</t>
+        </is>
+      </c>
+      <c r="H4" s="41" t="inlineStr">
+        <is>
+          <t>제약조건</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="38">
+      <c r="A5" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="50" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="C5" s="44" t="inlineStr">
+        <is>
+          <t>자료 식별 번호</t>
+        </is>
+      </c>
+      <c r="D5" s="51" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E5" s="51" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F5" s="51" t="inlineStr">
+        <is>
+          <t>자동생성</t>
+        </is>
+      </c>
+      <c r="G5" s="51" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="H5" s="51" t="inlineStr">
+        <is>
+          <t>기본키(PK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="38">
+      <c r="A6" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="50" t="inlineStr">
+        <is>
+          <t>작품_번호</t>
+        </is>
+      </c>
+      <c r="C6" s="44" t="inlineStr">
+        <is>
+          <t>작품 식별 번호</t>
+        </is>
+      </c>
+      <c r="D6" s="51" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E6" s="51" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F6" s="51" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G6" s="51" t="n"/>
+      <c r="H6" s="51" t="inlineStr">
+        <is>
+          <t>외래키(FK), 복합 UNIQUE(작품_번호, 순서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="38">
+      <c r="A7" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="50" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="C7" s="44" t="inlineStr">
+        <is>
+          <t>작품 내부 자료 번호</t>
+        </is>
+      </c>
+      <c r="D7" s="51" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E7" s="51" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F7" s="51" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G7" s="51" t="inlineStr">
+        <is>
+          <t>확정 스냅샷 안에서 이 글을 가리키는 번호</t>
+        </is>
+      </c>
+      <c r="H7" s="51" t="inlineStr">
+        <is>
+          <t>복합 UNIQUE(작품_번호, 순서), CHECK (순서 &gt;= 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="38">
+      <c r="A8" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="50" t="inlineStr">
+        <is>
+          <t>제목</t>
+        </is>
+      </c>
+      <c r="C8" s="44" t="inlineStr">
+        <is>
+          <t>제작자가 알아보기 위한 글 제목</t>
+        </is>
+      </c>
+      <c r="D8" s="51" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="E8" s="51" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F8" s="51" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G8" s="51" t="inlineStr">
+        <is>
+          <t>기믹과 설명 화면에서 글을 가리킬 때 쓴다</t>
+        </is>
+      </c>
+      <c r="H8" s="51" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="38">
+      <c r="A9" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="50" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="C9" s="44" t="inlineStr">
+        <is>
+          <t>글 본문</t>
+        </is>
+      </c>
+      <c r="D9" s="44" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="E9" s="44" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F9" s="44" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G9" s="44" t="n"/>
+      <c r="H9" s="44" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="J1" location="'목차'!A1" display="← 목차"/>
+  </hyperlinks>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="C29" s="42" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D29" s="44" t="n"/>
     </row>
@@ -7751,7 +7751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.62109375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="37" min="1" max="1"/>
@@ -7796,7 +7796,7 @@
       </c>
       <c r="B2" s="44" t="inlineStr">
         <is>
-          <t>게임 참여자의 게임 내용 기록 및 후기 테이블</t>
+          <t>게임 참여자의 플레이 기록(평점·난이도·후기·메모) 테이블</t>
         </is>
       </c>
       <c r="C2" s="47" t="n"/>
@@ -8054,17 +8054,17 @@
       </c>
       <c r="B10" s="50" t="inlineStr">
         <is>
-          <t>후기</t>
+          <t>평점</t>
         </is>
       </c>
       <c r="C10" s="55" t="inlineStr">
         <is>
-          <t>게임 종료 후 작성 후기</t>
+          <t>플레이어가 매긴 작품 평점</t>
         </is>
       </c>
       <c r="D10" s="55" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>NUMERIC(2,1)</t>
         </is>
       </c>
       <c r="E10" s="55" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="G10" s="55" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>0~5, 0.5 단위. NULL=기록 안 함(0과 다름). 후기를 비공개로 해도 평균에 반영</t>
         </is>
       </c>
       <c r="H10" s="55" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>CHECK (평점은 0 이상 5 이하, 0.5 단위)</t>
         </is>
       </c>
     </row>
@@ -8094,49 +8094,159 @@
       </c>
       <c r="B11" s="50" t="inlineStr">
         <is>
-          <t>비공개</t>
+          <t>난이도</t>
         </is>
       </c>
       <c r="C11" s="55" t="inlineStr">
         <is>
-          <t>후기의 공개여부</t>
+          <t>플레이어가 느낀 작품 난이도</t>
         </is>
       </c>
       <c r="D11" s="72" t="inlineStr">
         <is>
+          <t>NUMERIC(2,1)</t>
+        </is>
+      </c>
+      <c r="E11" s="55" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F11" s="55" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G11" s="55" t="inlineStr">
+        <is>
+          <t>0~5, 0.5 단위. NULL=기록 안 함(0과 다름). 후기를 비공개로 해도 평균에 반영</t>
+        </is>
+      </c>
+      <c r="H11" s="55" t="inlineStr">
+        <is>
+          <t>CHECK (난이도는 0 이상 5 이하, 0.5 단위)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16.5" customHeight="1" s="38">
+      <c r="A12" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="50" t="inlineStr">
+        <is>
+          <t>후기</t>
+        </is>
+      </c>
+      <c r="C12" s="55" t="inlineStr">
+        <is>
+          <t>게임 종료 후 작성 후기</t>
+        </is>
+      </c>
+      <c r="D12" s="55" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="E12" s="55" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F12" s="55" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G12" s="55" t="inlineStr">
+        <is>
+          <t>스포일러 표시는 글 안의 표시 문법으로 하며 DB에서 다루지 않음</t>
+        </is>
+      </c>
+      <c r="H12" s="55" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16.5" customHeight="1" s="38">
+      <c r="A13" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="50" t="inlineStr">
+        <is>
+          <t>후기공개</t>
+        </is>
+      </c>
+      <c r="C13" s="55" t="inlineStr">
+        <is>
+          <t>후기 글의 공개 여부</t>
+        </is>
+      </c>
+      <c r="D13" s="55" t="inlineStr">
+        <is>
           <t>BOOLEAN</t>
         </is>
       </c>
-      <c r="E11" s="55" t="inlineStr">
-        <is>
-          <t>불가</t>
-        </is>
-      </c>
-      <c r="F11" s="55" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G11" s="55" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="H11" s="55" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16.5" customHeight="1" s="38">
-      <c r="A12" s="56" t="n"/>
-      <c r="B12" s="56" t="n"/>
-      <c r="C12" s="56" t="n"/>
-      <c r="D12" s="56" t="n"/>
-      <c r="E12" s="56" t="n"/>
-      <c r="F12" s="56" t="n"/>
-      <c r="G12" s="56" t="n"/>
-      <c r="H12" s="56" t="n"/>
+      <c r="E13" s="55" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F13" s="55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G13" s="55" t="inlineStr">
+        <is>
+          <t>FALSE이면 작성자와 제작자만 볼 수 있음(서버가 보장). 평점·난이도에는 영향 없음</t>
+        </is>
+      </c>
+      <c r="H13" s="55" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16.5" customHeight="1" s="38">
+      <c r="A14" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="50" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+      <c r="C14" s="55" t="inlineStr">
+        <is>
+          <t>본인이 남기는 기록 메모</t>
+        </is>
+      </c>
+      <c r="D14" s="55" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="E14" s="55" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F14" s="55" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G14" s="55" t="inlineStr">
+        <is>
+          <t>본인만 볼 수 있음(서버가 본인에게만 내려 줌)</t>
+        </is>
+      </c>
+      <c r="H14" s="55" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="C22" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" s="44" t="n"/>
     </row>
@@ -4803,17 +4803,17 @@
       </c>
       <c r="B8" s="50" t="inlineStr">
         <is>
-          <t>조건</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="C8" s="44" t="inlineStr">
         <is>
-          <t>엔딩 진입 조건</t>
+          <t>엔딩 분기의 이름</t>
         </is>
       </c>
       <c r="D8" s="44" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="E8" s="44" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="G8" s="60" t="inlineStr">
         <is>
-          <t>게임 엔진 해석용 구조화 데이터</t>
+          <t>기록 화면 등에 "엔딩: ○○"으로 보여 줌. 나중에 바꿀 수 있음</t>
         </is>
       </c>
       <c r="H8" s="60" t="n"/>
@@ -4839,31 +4839,67 @@
       </c>
       <c r="B9" s="50" t="inlineStr">
         <is>
+          <t>조건</t>
+        </is>
+      </c>
+      <c r="C9" s="44" t="inlineStr">
+        <is>
+          <t>엔딩 진입 조건</t>
+        </is>
+      </c>
+      <c r="D9" s="44" t="inlineStr">
+        <is>
+          <t>JSONB</t>
+        </is>
+      </c>
+      <c r="E9" s="44" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F9" s="44" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G9" s="44" t="inlineStr">
+        <is>
+          <t>게임 엔진 해석용 구조화 데이터</t>
+        </is>
+      </c>
+      <c r="H9" s="60" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="38">
+      <c r="A10" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="50" t="inlineStr">
+        <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="C9" s="44" t="inlineStr">
+      <c r="C10" s="44" t="inlineStr">
         <is>
           <t>엔딩 내용</t>
         </is>
       </c>
-      <c r="D9" s="44" t="inlineStr">
+      <c r="D10" s="44" t="inlineStr">
         <is>
           <t>TEXT</t>
         </is>
       </c>
-      <c r="E9" s="44" t="inlineStr">
-        <is>
-          <t>불가</t>
-        </is>
-      </c>
-      <c r="F9" s="44" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="G9" s="44" t="n"/>
-      <c r="H9" s="60" t="n"/>
+      <c r="E10" s="44" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F10" s="44" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G10" s="44" t="n"/>
+      <c r="H10" s="60" t="n"/>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="38">
       <c r="B12" s="56" t="n"/>

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -1,45 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="30" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="목차" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="계정" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="로그인세션" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작품" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="버전" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="진행순서" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="진행구성" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기믹적용" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="미디어" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인물" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="관계" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장소" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="단서" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="증언" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="조합" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="조합재료" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사건" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사건설명" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="엔딩분기" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="후일담" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="타임라인" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="진행단계" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기믹" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="방" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="진행" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="참여" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기믹실행" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="투표" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="투표결과" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="엔딩" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="획득" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="테스터" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자료" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="목차" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="계정" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="로그인세션" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="작품" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="버전" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="진행순서" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="진행구성" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="기믹적용" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="미디어" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="인물" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="관계" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="장소" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="단서" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="증언" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="조합" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="조합재료" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="사건" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="사건설명" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="엔딩분기" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="후일담" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="타임라인" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="진행단계" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="기믹" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="방" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="진행" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="참여" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="기믹실행" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="투표" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="투표결과" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="엔딩" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="획득" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="테스터" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="자료" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" s="44" t="n"/>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="44" t="n"/>
     </row>
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" s="44" t="n"/>
     </row>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="H11" s="44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -12123,7 +12123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="37" min="1" max="1"/>
@@ -12340,33 +12340,73 @@
       </c>
       <c r="B8" s="50" t="inlineStr">
         <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="C8" s="44" t="inlineStr">
+        <is>
+          <t>플레이어에게 보이는 페이즈 이름</t>
+        </is>
+      </c>
+      <c r="D8" s="51" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="E8" s="44" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F8" s="44" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G8" s="44" t="inlineStr">
+        <is>
+          <t>제작자가 정함. 비우면 안의 진행단계 이름으로 보여 줌</t>
+        </is>
+      </c>
+      <c r="H8" s="44" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="50" t="inlineStr">
+        <is>
           <t>진행시간</t>
         </is>
       </c>
-      <c r="C8" s="44" t="inlineStr">
+      <c r="C9" s="44" t="inlineStr">
         <is>
           <t>해당 순서 진행 시간</t>
         </is>
       </c>
-      <c r="D8" s="44" t="inlineStr">
+      <c r="D9" s="44" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="E8" s="44" t="inlineStr">
-        <is>
-          <t>불가</t>
-        </is>
-      </c>
-      <c r="F8" s="44" t="n">
+      <c r="E9" s="44" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F9" s="44" t="n">
         <v>30</v>
       </c>
-      <c r="G8" s="44" t="inlineStr">
+      <c r="G9" s="44" t="inlineStr">
         <is>
           <t>분 단위로 저장</t>
         </is>
       </c>
-      <c r="H8" s="44" t="inlineStr">
+      <c r="H9" s="44" t="inlineStr">
         <is>
           <t>CHECK (진행시간 &gt;= 0)</t>
         </is>
@@ -12392,7 +12432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="37" min="1" max="1"/>
@@ -12634,6 +12674,46 @@
       <c r="H8" s="44" t="inlineStr">
         <is>
           <t>외래키(FK), 복합 UNIQUE (작품_번호, 진행순서_순서, 진행단계_번호)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="38">
+      <c r="A9" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="50" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="C9" s="44" t="inlineStr">
+        <is>
+          <t>칸에 놓은 카드의 세부 설정</t>
+        </is>
+      </c>
+      <c r="D9" s="51" t="inlineStr">
+        <is>
+          <t>JSONB</t>
+        </is>
+      </c>
+      <c r="E9" s="44" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F9" s="44" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G9" s="44" t="inlineStr">
+        <is>
+          <t>NULL=진행단계 정의의 기본값을 씀. 탭을 남길지 등. 내부 구조는 엔진 설계에서 정함</t>
+        </is>
+      </c>
+      <c r="H9" s="44" t="inlineStr">
+        <is>
+          <t>없음</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.62109375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="37" min="1" max="1"/>
@@ -12935,6 +13015,46 @@
       <c r="H9" s="55" t="inlineStr">
         <is>
           <t>복합 외래키(작품_번호, 진행순서_순서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="38">
+      <c r="A10" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="50" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="C10" s="44" t="inlineStr">
+        <is>
+          <t>칸에 붙인 기믹의 세부 설정</t>
+        </is>
+      </c>
+      <c r="D10" s="51" t="inlineStr">
+        <is>
+          <t>JSONB</t>
+        </is>
+      </c>
+      <c r="E10" s="51" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F10" s="44" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G10" s="44" t="inlineStr">
+        <is>
+          <t>NULL=기믹 정의의 기본값을 씀. 내부 구조는 엔진 설계에서 정함</t>
+        </is>
+      </c>
+      <c r="H10" s="55" t="inlineStr">
+        <is>
+          <t>없음</t>
         </is>
       </c>
     </row>

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -755,6 +755,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16.5" customHeight="1" s="38">
       <c r="A4" s="41" t="inlineStr">
         <is>
@@ -899,7 +900,7 @@
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D13" s="44" t="n"/>
     </row>
@@ -1271,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.62109375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="37" min="1" max="1"/>
@@ -1831,6 +1832,38 @@
       </c>
       <c r="G18" s="44" t="n"/>
       <c r="H18" s="44" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="42" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="50" t="inlineStr">
+        <is>
+          <t>소개</t>
+        </is>
+      </c>
+      <c r="C19" s="55" t="inlineStr">
+        <is>
+          <t>자기소개 단계에서 보여 주는 인물 소개 멘트</t>
+        </is>
+      </c>
+      <c r="D19" s="44" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="E19" s="44" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F19" s="44" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G19" s="44" t="n"/>
+      <c r="H19" s="44" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -38,8 +38,9 @@
     <sheet name="투표결과" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="엔딩" sheetId="30" state="visible" r:id="rId30"/>
     <sheet name="획득" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="테스터" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="자료" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="공개" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="테스터" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="자료" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -731,7 +732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="37" min="1" max="1"/>
@@ -755,7 +756,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16.5" customHeight="1" s="38">
       <c r="A4" s="41" t="inlineStr">
         <is>
@@ -1204,11 +1204,11 @@
       </c>
       <c r="B35" s="43" t="inlineStr">
         <is>
-          <t>테스터</t>
+          <t>공개</t>
         </is>
       </c>
       <c r="C35" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D35" s="44" t="n"/>
     </row>
@@ -1218,47 +1218,63 @@
       </c>
       <c r="B36" s="43" t="inlineStr">
         <is>
+          <t>테스터</t>
+        </is>
+      </c>
+      <c r="C36" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" s="44" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="42" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="43" t="inlineStr">
+        <is>
           <t>자료</t>
         </is>
       </c>
-      <c r="C36" s="42" t="n">
+      <c r="C37" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="D36" s="44" t="n"/>
+      <c r="D37" s="44" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B5" location="'계정'!A1" display="계정"/>
-    <hyperlink ref="B6" location="'로그인세션'!A1" display="로그인세션"/>
-    <hyperlink ref="B7" location="'작품'!A1" display="작품"/>
-    <hyperlink ref="B8" location="'버전'!A1" display="버전"/>
-    <hyperlink ref="B9" location="'진행순서'!A1" display="진행순서"/>
-    <hyperlink ref="B10" location="'진행구성'!A1" display="진행구성"/>
-    <hyperlink ref="B11" location="'기믹적용'!A1" display="기믹적용"/>
-    <hyperlink ref="B12" location="'미디어'!A1" display="미디어"/>
-    <hyperlink ref="B13" location="'인물'!A1" display="인물"/>
-    <hyperlink ref="B14" location="'관계'!A1" display="관계"/>
-    <hyperlink ref="B15" location="'장소'!A1" display="장소"/>
-    <hyperlink ref="B16" location="'단서'!A1" display="단서"/>
-    <hyperlink ref="B17" location="'증언'!A1" display="증언"/>
-    <hyperlink ref="B18" location="'조합'!A1" display="조합"/>
-    <hyperlink ref="B19" location="'조합재료'!A1" display="조합재료"/>
-    <hyperlink ref="B20" location="'사건'!A1" display="사건"/>
-    <hyperlink ref="B21" location="'사건설명'!A1" display="사건설명"/>
-    <hyperlink ref="B22" location="'엔딩분기'!A1" display="엔딩분기"/>
-    <hyperlink ref="B23" location="'후일담'!A1" display="후일담"/>
-    <hyperlink ref="B24" location="'타임라인'!A1" display="타임라인"/>
-    <hyperlink ref="B25" location="'진행단계'!A1" display="진행단계"/>
-    <hyperlink ref="B26" location="'기믹'!A1" display="기믹"/>
-    <hyperlink ref="B27" location="'방'!A1" display="방"/>
-    <hyperlink ref="B28" location="'진행'!A1" display="진행"/>
-    <hyperlink ref="B29" location="'참여'!A1" display="참여"/>
-    <hyperlink ref="B30" location="'기믹실행'!A1" display="기믹실행"/>
-    <hyperlink ref="B32" location="'투표결과'!A1" display="투표결과"/>
-    <hyperlink ref="B33" location="'엔딩'!A1" display="엔딩"/>
-    <hyperlink ref="B34" location="'획득'!A1" display="획득"/>
-    <hyperlink ref="B35" location="'테스터'!A1" display="테스터"/>
-    <hyperlink ref="B36" location="'자료'!A1" display="자료"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" location="'계정'!A1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" location="'로그인세션'!A1" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" location="'작품'!A1" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" location="'버전'!A1" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" location="'진행순서'!A1" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" location="'진행구성'!A1" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" location="'기믹적용'!A1" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" location="'미디어'!A1" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" location="'인물'!A1" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" location="'관계'!A1" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" location="'장소'!A1" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" location="'단서'!A1" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" location="'증언'!A1" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" location="'조합'!A1" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" location="'조합재료'!A1" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" location="'사건'!A1" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" location="'사건설명'!A1" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" location="'엔딩분기'!A1" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" location="'후일담'!A1" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" location="'타임라인'!A1" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" location="'진행단계'!A1" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" location="'기믹'!A1" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" location="'방'!A1" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" location="'진행'!A1" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" location="'참여'!A1" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" location="'기믹실행'!A1" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" location="'투표'!A1" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" location="'투표결과'!A1" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" location="'엔딩'!A1" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" location="'획득'!A1" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" location="'공개'!A1" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" location="'테스터'!A1" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" location="'자료'!A1" r:id="rId33"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4934,6 +4950,7 @@
       <c r="G10" s="44" t="n"/>
       <c r="H10" s="60" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12" ht="16.5" customHeight="1" s="38">
       <c r="B12" s="56" t="n"/>
       <c r="C12" s="56" t="n"/>
@@ -10572,6 +10589,401 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.62109375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="14" customWidth="1" style="37" min="1" max="1"/>
+    <col width="24" customWidth="1" style="37" min="2" max="2"/>
+    <col width="40" customWidth="1" style="37" min="3" max="3"/>
+    <col width="16" customWidth="1" style="37" min="4" max="4"/>
+    <col width="12" customWidth="1" style="37" min="5" max="5"/>
+    <col width="14" customWidth="1" style="37" min="6" max="6"/>
+    <col width="40" customWidth="1" style="37" min="7" max="7"/>
+    <col width="97.84" customWidth="1" style="37" min="8" max="8"/>
+    <col width="8.619999999999999" customWidth="1" style="37" min="9" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.5" customHeight="1" s="38">
+      <c r="A1" s="45" t="inlineStr">
+        <is>
+          <t>테이블명</t>
+        </is>
+      </c>
+      <c r="B1" s="46" t="inlineStr">
+        <is>
+          <t>공개</t>
+        </is>
+      </c>
+      <c r="C1" s="47" t="n"/>
+      <c r="D1" s="47" t="n"/>
+      <c r="E1" s="47" t="n"/>
+      <c r="F1" s="47" t="n"/>
+      <c r="G1" s="47" t="n"/>
+      <c r="H1" s="48" t="n"/>
+      <c r="J1" s="49" t="inlineStr">
+        <is>
+          <t>← 목차</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1" s="38">
+      <c r="A2" s="45" t="inlineStr">
+        <is>
+          <t>테이블 설명</t>
+        </is>
+      </c>
+      <c r="B2" s="44" t="inlineStr">
+        <is>
+          <t>게임 중 단서를 다른 참가자에게 보여 준 기록(대상이 비어 있으면 전체 공개, 취소일시가 비어 있으면 유효)</t>
+        </is>
+      </c>
+      <c r="C2" s="47" t="n"/>
+      <c r="D2" s="47" t="n"/>
+      <c r="E2" s="47" t="n"/>
+      <c r="F2" s="47" t="n"/>
+      <c r="G2" s="47" t="n"/>
+      <c r="H2" s="48" t="n"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="38">
+      <c r="A4" s="41" t="inlineStr">
+        <is>
+          <t>순번</t>
+        </is>
+      </c>
+      <c r="B4" s="41" t="inlineStr">
+        <is>
+          <t>컬럼명</t>
+        </is>
+      </c>
+      <c r="C4" s="41" t="inlineStr">
+        <is>
+          <t>컬럼 설명</t>
+        </is>
+      </c>
+      <c r="D4" s="41" t="inlineStr">
+        <is>
+          <t>데이터타입</t>
+        </is>
+      </c>
+      <c r="E4" s="41" t="inlineStr">
+        <is>
+          <t>Null허용</t>
+        </is>
+      </c>
+      <c r="F4" s="41" t="inlineStr">
+        <is>
+          <t>기본값</t>
+        </is>
+      </c>
+      <c r="G4" s="41" t="inlineStr">
+        <is>
+          <t>특징</t>
+        </is>
+      </c>
+      <c r="H4" s="41" t="inlineStr">
+        <is>
+          <t>제약조건</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="38">
+      <c r="A5" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="50" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>공개 식별 번호</t>
+        </is>
+      </c>
+      <c r="D5" s="64" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E5" s="64" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F5" s="64" t="inlineStr">
+        <is>
+          <t>자동생성</t>
+        </is>
+      </c>
+      <c r="G5" s="64" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="H5" s="64" t="inlineStr">
+        <is>
+          <t>기본키(PK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="38">
+      <c r="A6" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="50" t="inlineStr">
+        <is>
+          <t>작품_번호</t>
+        </is>
+      </c>
+      <c r="C6" s="55" t="inlineStr">
+        <is>
+          <t>작품 식별 번호</t>
+        </is>
+      </c>
+      <c r="D6" s="64" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E6" s="55" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F6" s="55" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G6" s="55" t="n"/>
+      <c r="H6" s="55" t="inlineStr">
+        <is>
+          <t>외래키(FK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="38">
+      <c r="A7" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="50" t="inlineStr">
+        <is>
+          <t>진행_번호</t>
+        </is>
+      </c>
+      <c r="C7" s="55" t="inlineStr">
+        <is>
+          <t>게임 진행 식별 번호</t>
+        </is>
+      </c>
+      <c r="D7" s="64" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E7" s="55" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F7" s="55" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G7" s="55" t="n"/>
+      <c r="H7" s="55" t="inlineStr">
+        <is>
+          <t>외래키(FK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="38">
+      <c r="A8" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="50" t="inlineStr">
+        <is>
+          <t>획득_번호</t>
+        </is>
+      </c>
+      <c r="C8" s="55" t="inlineStr">
+        <is>
+          <t>공개한 단서의 획득 식별 번호</t>
+        </is>
+      </c>
+      <c r="D8" s="64" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E8" s="55" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F8" s="55" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G8" s="55" t="n"/>
+      <c r="H8" s="55" t="inlineStr">
+        <is>
+          <t>외래키(FK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="38">
+      <c r="A9" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="50" t="inlineStr">
+        <is>
+          <t>대상_참여_번호</t>
+        </is>
+      </c>
+      <c r="C9" s="55" t="inlineStr">
+        <is>
+          <t>공개 대상 참가자의 식별 번호(없으면 전체 공개)</t>
+        </is>
+      </c>
+      <c r="D9" s="64" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E9" s="55" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F9" s="55" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G9" s="55" t="n"/>
+      <c r="H9" s="66" t="inlineStr">
+        <is>
+          <t>외래키(FK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="38">
+      <c r="A10" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="50" t="inlineStr">
+        <is>
+          <t>공개일시</t>
+        </is>
+      </c>
+      <c r="C10" s="55" t="inlineStr">
+        <is>
+          <t>공개한 시각</t>
+        </is>
+      </c>
+      <c r="D10" s="64" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="E10" s="55" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F10" s="55" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G10" s="55" t="n"/>
+      <c r="H10" s="66" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="38">
+      <c r="A11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="50" t="inlineStr">
+        <is>
+          <t>취소일시</t>
+        </is>
+      </c>
+      <c r="C11" s="55" t="inlineStr">
+        <is>
+          <t>공개를 취소한 시각(없으면 유효)</t>
+        </is>
+      </c>
+      <c r="D11" s="64" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="E11" s="55" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F11" s="55" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G11" s="55" t="n"/>
+      <c r="H11" s="66" t="n"/>
+    </row>
+    <row r="12" ht="16.5" customHeight="1" s="38">
+      <c r="A12" s="42" t="n"/>
+      <c r="B12" s="50" t="n"/>
+      <c r="C12" s="55" t="n"/>
+      <c r="D12" s="64" t="n"/>
+      <c r="E12" s="55" t="n"/>
+      <c r="F12" s="55" t="n"/>
+      <c r="G12" s="55" t="n"/>
+      <c r="H12" s="66" t="n"/>
+    </row>
+    <row r="13" ht="16.5" customHeight="1" s="38">
+      <c r="A13" s="42" t="n"/>
+      <c r="B13" s="50" t="n"/>
+      <c r="C13" s="55" t="n"/>
+      <c r="D13" s="55" t="n"/>
+      <c r="E13" s="55" t="n"/>
+      <c r="F13" s="55" t="n"/>
+      <c r="G13" s="55" t="n"/>
+      <c r="H13" s="55" t="n"/>
+    </row>
+    <row r="14" ht="16.5" customHeight="1" s="38">
+      <c r="A14" s="42" t="n"/>
+      <c r="B14" s="50" t="n"/>
+      <c r="C14" s="55" t="n"/>
+      <c r="D14" s="55" t="n"/>
+      <c r="E14" s="55" t="n"/>
+      <c r="F14" s="55" t="n"/>
+      <c r="G14" s="55" t="n"/>
+      <c r="H14" s="55" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="J1" location="'목차'!A1" display="← 목차"/>
+  </hyperlinks>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.62109375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
@@ -10883,7 +11295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -4950,7 +4950,6 @@
       <c r="G10" s="44" t="n"/>
       <c r="H10" s="60" t="n"/>
     </row>
-    <row r="11"/>
     <row r="12" ht="16.5" customHeight="1" s="38">
       <c r="B12" s="56" t="n"/>
       <c r="C12" s="56" t="n"/>
@@ -7155,7 +7154,7 @@
       </c>
       <c r="C7" s="44" t="inlineStr">
         <is>
-          <t>방 입장 코드</t>
+          <t>방 입장 코드(방장이 정함)</t>
         </is>
       </c>
       <c r="D7" s="44" t="inlineStr">
@@ -7173,12 +7172,12 @@
           <t>없음</t>
         </is>
       </c>
-      <c r="G7" s="44" t="n"/>
-      <c r="H7" s="60" t="inlineStr">
-        <is>
-          <t>UNIQUE</t>
-        </is>
-      </c>
+      <c r="G7" s="44" t="inlineStr">
+        <is>
+          <t>종료되지 않은(대기·진행) 방 사이에서만 유일. 종료된 방의 코드는 다시 쓸 수 있음(부분 유일 인덱스 uq_방_입장코드_사용중)</t>
+        </is>
+      </c>
+      <c r="H7" s="60" t="n"/>
     </row>
     <row r="8" ht="16.5" customHeight="1" s="38">
       <c r="A8" s="42" t="n">

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="44" t="n"/>
     </row>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" s="44" t="n"/>
     </row>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="C18" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" s="44" t="n"/>
     </row>
@@ -2559,7 +2559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.62109375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="37" min="1" max="1"/>
@@ -2935,6 +2935,38 @@
           <t>복합 외래키(작품_번호, 장소_순서)</t>
         </is>
       </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="50" t="inlineStr">
+        <is>
+          <t>공개이름</t>
+        </is>
+      </c>
+      <c r="C13" s="55" t="inlineStr">
+        <is>
+          <t>남들에게 보여 주는 이름(위치를 뜻하는 겉이름)</t>
+        </is>
+      </c>
+      <c r="D13" s="64" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="E13" s="55" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F13" s="55" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G13" s="55" t="n"/>
+      <c r="H13" s="55" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2956,7 +2988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.62109375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="37" min="1" max="1"/>
@@ -3171,12 +3203,12 @@
       </c>
       <c r="B8" s="50" t="inlineStr">
         <is>
-          <t>화자</t>
+          <t>공개이름</t>
         </is>
       </c>
       <c r="C8" s="55" t="inlineStr">
         <is>
-          <t>증언의 화자</t>
+          <t>남들에게 보여 주는 이름(예: 지나가던 사람)</t>
         </is>
       </c>
       <c r="D8" s="55" t="inlineStr">
@@ -3186,7 +3218,7 @@
       </c>
       <c r="E8" s="55" t="inlineStr">
         <is>
-          <t>불가</t>
+          <t>가능</t>
         </is>
       </c>
       <c r="F8" s="55" t="inlineStr">
@@ -3300,6 +3332,38 @@
           <t>복합 외래키(작품_번호, 장소_순서)</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="50" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="C12" s="55" t="inlineStr">
+        <is>
+          <t>증언의 진짜 이름(예: A의 마약소문)</t>
+        </is>
+      </c>
+      <c r="D12" s="64" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="E12" s="55" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F12" s="55" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G12" s="55" t="n"/>
+      <c r="H12" s="66" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3321,7 +3385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.62109375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="37" min="1" max="1"/>
@@ -3625,6 +3689,38 @@
       </c>
       <c r="G10" s="55" t="n"/>
       <c r="H10" s="55" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="50" t="inlineStr">
+        <is>
+          <t>공개이름</t>
+        </is>
+      </c>
+      <c r="C11" s="55" t="inlineStr">
+        <is>
+          <t>남들에게 보여 주는 이름(위치를 뜻하는 겉이름)</t>
+        </is>
+      </c>
+      <c r="D11" s="55" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="E11" s="55" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F11" s="55" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G11" s="55" t="n"/>
+      <c r="H11" s="55" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4950,6 +5046,7 @@
       <c r="G10" s="44" t="n"/>
       <c r="H10" s="60" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12" ht="16.5" customHeight="1" s="38">
       <c r="B12" s="56" t="n"/>
       <c r="C12" s="56" t="n"/>

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -1,46 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="30" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="목차" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="계정" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="로그인세션" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="작품" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="버전" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="진행순서" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="진행구성" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="기믹적용" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="미디어" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="인물" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="관계" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="장소" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="단서" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="증언" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="조합" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="조합재료" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="사건" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="사건설명" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="엔딩분기" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="후일담" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="타임라인" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="진행단계" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="기믹" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="방" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="진행" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="참여" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="기믹실행" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="투표" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="투표결과" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="엔딩" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="획득" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="공개" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="테스터" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="자료" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="목차" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="계정" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="로그인세션" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작품" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="버전" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="진행순서" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="진행구성" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기믹적용" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="미디어" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인물" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="관계" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장소" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="단서" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="증언" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="조합" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="조합재료" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사건" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사건설명" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="엔딩분기" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="후일담" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="타임라인" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="진행단계" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기믹" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="방" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="진행" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="참여" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기믹실행" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="투표" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="투표결과" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="엔딩" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="획득" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공개" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="테스터" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자료" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -756,6 +756,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16.5" customHeight="1" s="38">
       <c r="A4" s="41" t="inlineStr">
         <is>
@@ -900,7 +901,7 @@
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D13" s="44" t="n"/>
     </row>
@@ -1288,7 +1289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.62109375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="37" min="1" max="1"/>
@@ -1880,6 +1881,74 @@
       </c>
       <c r="G19" s="44" t="n"/>
       <c r="H19" s="44" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="50" t="inlineStr">
+        <is>
+          <t>선택소개</t>
+        </is>
+      </c>
+      <c r="C20" s="55" t="inlineStr">
+        <is>
+          <t>캐릭터 선택 단계에서 보여 줄 수 있는 소개</t>
+        </is>
+      </c>
+      <c r="D20" s="44" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="E20" s="44" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F20" s="44" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G20" s="44" t="n"/>
+      <c r="H20" s="44" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="42" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="50" t="inlineStr">
+        <is>
+          <t>NPC순위</t>
+        </is>
+      </c>
+      <c r="C21" s="55" t="inlineStr">
+        <is>
+          <t>인원이 모자랄 때 NPC 가 되는 순서(1 이 먼저). 값이 있으면 NPC 가 될 수 있는 인물</t>
+        </is>
+      </c>
+      <c r="D21" s="44" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E21" s="44" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F21" s="44" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G21" s="44" t="n"/>
+      <c r="H21" s="44" t="inlineStr">
+        <is>
+          <t>CHECK (NPC순위 IS NULL OR (NPC순위 &gt;= 1 AND NOT NPC)), 부분 UNIQUE(작품_번호, NPC순위) WHERE NPC순위 IS NOT NULL</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5046,7 +5115,6 @@
       <c r="G10" s="44" t="n"/>
       <c r="H10" s="60" t="n"/>
     </row>
-    <row r="11"/>
     <row r="12" ht="16.5" customHeight="1" s="38">
       <c r="B12" s="56" t="n"/>
       <c r="C12" s="56" t="n"/>
@@ -7420,7 +7488,7 @@
       </c>
       <c r="H11" s="44" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -756,7 +756,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16.5" customHeight="1" s="38">
       <c r="A4" s="41" t="inlineStr">
         <is>
@@ -1888,12 +1887,12 @@
       </c>
       <c r="B20" s="50" t="inlineStr">
         <is>
-          <t>선택소개</t>
+          <t>캐릭터설명</t>
         </is>
       </c>
       <c r="C20" s="55" t="inlineStr">
         <is>
-          <t>캐릭터 선택 단계에서 보여 줄 수 있는 소개</t>
+          <t>캐릭터 선택 화면과 캐릭터 설명 탭에 보여 줄 수 있는 인물 설명</t>
         </is>
       </c>
       <c r="D20" s="44" t="inlineStr">

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -9270,6 +9270,7 @@
       <c r="G2" s="47" t="n"/>
       <c r="H2" s="48" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="16.5" customHeight="1" s="38">
       <c r="A4" s="41" t="inlineStr">
         <is>
@@ -9394,17 +9395,17 @@
       </c>
       <c r="B7" s="50" t="inlineStr">
         <is>
-          <t>투표_순서</t>
+          <t>투표이름</t>
         </is>
       </c>
       <c r="C7" s="44" t="inlineStr">
         <is>
-          <t>작품 내부 투표 번호</t>
+          <t>게임에서 투표를 구분하는 이름(예: 최종 투표)</t>
         </is>
       </c>
       <c r="D7" s="75" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="E7" s="60" t="inlineStr">
@@ -9418,11 +9419,7 @@
         </is>
       </c>
       <c r="G7" s="60" t="n"/>
-      <c r="H7" s="67" t="inlineStr">
-        <is>
-          <t>버전 시나리오 참조 검증</t>
-        </is>
-      </c>
+      <c r="H7" s="67" t="n"/>
     </row>
     <row r="8" ht="16.5" customHeight="1" s="38">
       <c r="A8" s="42" t="n">
@@ -9456,7 +9453,7 @@
       <c r="G8" s="60" t="n"/>
       <c r="H8" s="60" t="inlineStr">
         <is>
-          <t xml:space="preserve">외래키(FK), 복합 UNIQUE(작품_번호, 투표_순서, 참여_번호) </t>
+          <t xml:space="preserve">외래키(FK), 복합 UNIQUE(작품_번호, 투표이름, 참여_번호) </t>
         </is>
       </c>
     </row>

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -9270,7 +9270,6 @@
       <c r="G2" s="47" t="n"/>
       <c r="H2" s="48" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4" ht="16.5" customHeight="1" s="38">
       <c r="A4" s="41" t="inlineStr">
         <is>
@@ -11762,7 +11761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="37" min="1" max="1"/>
@@ -11817,6 +11816,7 @@
       <c r="G2" s="47" t="n"/>
       <c r="H2" s="48" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="16.5" customHeight="1" s="38">
       <c r="A4" s="41" t="inlineStr">
         <is>
@@ -12374,6 +12374,46 @@
         </is>
       </c>
       <c r="H19" s="44" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="50" t="inlineStr">
+        <is>
+          <t>시간형식</t>
+        </is>
+      </c>
+      <c r="C20" s="44" t="inlineStr">
+        <is>
+          <t>시간(타임라인 등)을 어디까지 적을지</t>
+        </is>
+      </c>
+      <c r="D20" s="44" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="E20" s="44" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F20" s="53" t="inlineStr">
+        <is>
+          <t>'시간만'</t>
+        </is>
+      </c>
+      <c r="G20" s="44" t="inlineStr">
+        <is>
+          <t>시간만 / 일까지 / 월까지 / 연도까지. 적지 않는 윗단위(연·월·일)는 2000-01-01 로 채워 TIMESTAMP 에 저장한다. 이미 있던 작품은 연도까지로 시작했다</t>
+        </is>
+      </c>
+      <c r="H20" s="44" t="inlineStr">
+        <is>
+          <t>CHECK (시간형식 IN ('시간만', '일까지', '월까지', '연도까지'))</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -12110,7 +12110,7 @@
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>개발 단계 표시</t>
+          <t>개발 단계 표시. 삭제는 플레이 기록이 있는 작품을 지웠을 때 남겨 두는 숨김 상태</t>
         </is>
       </c>
       <c r="D12" s="44" t="inlineStr">
@@ -12131,7 +12131,7 @@
       <c r="G12" s="44" t="n"/>
       <c r="H12" s="44" t="inlineStr">
         <is>
-          <t>CHECK (상태 IN ('수정', '개발', '완료'))</t>
+          <t>CHECK (상태 IN ('수정', '개발', '완료', '삭제'))</t>
         </is>
       </c>
     </row>

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -41,6 +41,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공개" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="테스터" sheetId="33" state="visible" r:id="rId33"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자료" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대화" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대화수신" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -732,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="37" min="1" max="1"/>
@@ -1239,6 +1241,34 @@
         <v>5</v>
       </c>
       <c r="D37" s="44" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="42" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="43" t="inlineStr">
+        <is>
+          <t>대화</t>
+        </is>
+      </c>
+      <c r="C38" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="D38" s="44" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="42" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="43" t="inlineStr">
+        <is>
+          <t>대화수신</t>
+        </is>
+      </c>
+      <c r="C39" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" s="44" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1275,6 +1305,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" location="'공개'!A1" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" location="'테스터'!A1" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" location="'자료'!A1" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" location="'대화'!A1" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" location="'대화수신'!A1" r:id="rId35"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11755,6 +11787,670 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.62109375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="14" customWidth="1" style="37" min="1" max="1"/>
+    <col width="24" customWidth="1" style="37" min="2" max="2"/>
+    <col width="40" customWidth="1" style="37" min="3" max="3"/>
+    <col width="16" customWidth="1" style="37" min="4" max="4"/>
+    <col width="12" customWidth="1" style="37" min="5" max="5"/>
+    <col width="18.62" customWidth="1" style="37" min="6" max="6"/>
+    <col width="40" customWidth="1" style="37" min="7" max="7"/>
+    <col width="57.02" customWidth="1" style="37" min="8" max="8"/>
+    <col width="8.619999999999999" customWidth="1" style="37" min="9" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.5" customHeight="1" s="38">
+      <c r="A1" s="45" t="inlineStr">
+        <is>
+          <t>테이블명</t>
+        </is>
+      </c>
+      <c r="B1" s="46" t="inlineStr">
+        <is>
+          <t>대화</t>
+        </is>
+      </c>
+      <c r="C1" s="47" t="n"/>
+      <c r="D1" s="47" t="n"/>
+      <c r="E1" s="47" t="n"/>
+      <c r="F1" s="47" t="n"/>
+      <c r="G1" s="47" t="n"/>
+      <c r="H1" s="48" t="n"/>
+      <c r="J1" s="49" t="inlineStr">
+        <is>
+          <t>← 목차</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1" s="38">
+      <c r="A2" s="45" t="inlineStr">
+        <is>
+          <t>테이블 설명</t>
+        </is>
+      </c>
+      <c r="B2" s="44" t="inlineStr">
+        <is>
+          <t>게임 채팅 메시지 기록 테이블(장소별, 전체·밀담)</t>
+        </is>
+      </c>
+      <c r="C2" s="47" t="n"/>
+      <c r="D2" s="47" t="n"/>
+      <c r="E2" s="47" t="n"/>
+      <c r="F2" s="47" t="n"/>
+      <c r="G2" s="47" t="n"/>
+      <c r="H2" s="48" t="n"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="38">
+      <c r="A4" s="41" t="inlineStr">
+        <is>
+          <t>순번</t>
+        </is>
+      </c>
+      <c r="B4" s="41" t="inlineStr">
+        <is>
+          <t>컬럼명</t>
+        </is>
+      </c>
+      <c r="C4" s="41" t="inlineStr">
+        <is>
+          <t>컬럼 설명</t>
+        </is>
+      </c>
+      <c r="D4" s="41" t="inlineStr">
+        <is>
+          <t>데이터타입</t>
+        </is>
+      </c>
+      <c r="E4" s="41" t="inlineStr">
+        <is>
+          <t>Null허용</t>
+        </is>
+      </c>
+      <c r="F4" s="41" t="inlineStr">
+        <is>
+          <t>기본값</t>
+        </is>
+      </c>
+      <c r="G4" s="41" t="inlineStr">
+        <is>
+          <t>특징</t>
+        </is>
+      </c>
+      <c r="H4" s="41" t="inlineStr">
+        <is>
+          <t>제약조건</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="38">
+      <c r="A5" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="50" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>대화 식별 번호</t>
+        </is>
+      </c>
+      <c r="D5" s="64" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E5" s="64" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F5" s="64" t="inlineStr">
+        <is>
+          <t>자동생성</t>
+        </is>
+      </c>
+      <c r="G5" s="64" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="H5" s="64" t="inlineStr">
+        <is>
+          <t>기본키(PK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="38">
+      <c r="A6" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="50" t="inlineStr">
+        <is>
+          <t>진행_번호</t>
+        </is>
+      </c>
+      <c r="C6" s="55" t="inlineStr">
+        <is>
+          <t>메시지가 오간 게임 진행 식별 번호</t>
+        </is>
+      </c>
+      <c r="D6" s="64" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E6" s="64" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F6" s="64" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G6" s="64" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H6" s="64" t="inlineStr">
+        <is>
+          <t>외래키(FK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="38">
+      <c r="A7" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="50" t="inlineStr">
+        <is>
+          <t>계정_번호</t>
+        </is>
+      </c>
+      <c r="C7" s="55" t="inlineStr">
+        <is>
+          <t>메시지를 보낸 계정 식별 번호</t>
+        </is>
+      </c>
+      <c r="D7" s="64" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E7" s="64" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F7" s="64" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G7" s="64" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H7" s="64" t="inlineStr">
+        <is>
+          <t>외래키(FK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="38">
+      <c r="A8" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="50" t="inlineStr">
+        <is>
+          <t>장소</t>
+        </is>
+      </c>
+      <c r="C8" s="55" t="inlineStr">
+        <is>
+          <t>메시지를 보낸 채팅 장소(전체, 밀담 A 등)</t>
+        </is>
+      </c>
+      <c r="D8" s="64" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="E8" s="64" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F8" s="64" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G8" s="64" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H8" s="64" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="38">
+      <c r="A9" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="50" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="C9" s="55" t="inlineStr">
+        <is>
+          <t>메시지 내용(1~500자)</t>
+        </is>
+      </c>
+      <c r="D9" s="64" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="E9" s="64" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F9" s="64" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G9" s="64" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H9" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHECK (char_length(내용) BETWEEN 1 AND 500) </t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="38">
+      <c r="A10" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="50" t="inlineStr">
+        <is>
+          <t>보낸일시</t>
+        </is>
+      </c>
+      <c r="C10" s="55" t="inlineStr">
+        <is>
+          <t>메시지를 보낸 일시</t>
+        </is>
+      </c>
+      <c r="D10" s="64" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="E10" s="64" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F10" s="64" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G10" s="64" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H10" s="64" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="38">
+      <c r="A11" s="42" t="n"/>
+      <c r="B11" s="50" t="n"/>
+      <c r="C11" s="55" t="n"/>
+      <c r="D11" s="72" t="n"/>
+      <c r="E11" s="55" t="n"/>
+      <c r="F11" s="55" t="n"/>
+      <c r="G11" s="55" t="n"/>
+      <c r="H11" s="55" t="n"/>
+    </row>
+    <row r="12" ht="16.5" customHeight="1" s="38">
+      <c r="A12" s="56" t="n"/>
+      <c r="B12" s="56" t="n"/>
+      <c r="C12" s="56" t="n"/>
+      <c r="D12" s="56" t="n"/>
+      <c r="E12" s="56" t="n"/>
+      <c r="F12" s="56" t="n"/>
+      <c r="G12" s="56" t="n"/>
+      <c r="H12" s="56" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1" location="'목차'!A1" r:id="rId1"/>
+  </hyperlinks>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.62109375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="14" customWidth="1" style="37" min="1" max="1"/>
+    <col width="24" customWidth="1" style="37" min="2" max="2"/>
+    <col width="40" customWidth="1" style="37" min="3" max="3"/>
+    <col width="16" customWidth="1" style="37" min="4" max="4"/>
+    <col width="12" customWidth="1" style="37" min="5" max="5"/>
+    <col width="18.62" customWidth="1" style="37" min="6" max="6"/>
+    <col width="40" customWidth="1" style="37" min="7" max="7"/>
+    <col width="57.02" customWidth="1" style="37" min="8" max="8"/>
+    <col width="8.619999999999999" customWidth="1" style="37" min="9" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.5" customHeight="1" s="38">
+      <c r="A1" s="45" t="inlineStr">
+        <is>
+          <t>테이블명</t>
+        </is>
+      </c>
+      <c r="B1" s="46" t="inlineStr">
+        <is>
+          <t>대화수신</t>
+        </is>
+      </c>
+      <c r="C1" s="47" t="n"/>
+      <c r="D1" s="47" t="n"/>
+      <c r="E1" s="47" t="n"/>
+      <c r="F1" s="47" t="n"/>
+      <c r="G1" s="47" t="n"/>
+      <c r="H1" s="48" t="n"/>
+      <c r="J1" s="49" t="inlineStr">
+        <is>
+          <t>← 목차</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1" s="38">
+      <c r="A2" s="45" t="inlineStr">
+        <is>
+          <t>테이블 설명</t>
+        </is>
+      </c>
+      <c r="B2" s="44" t="inlineStr">
+        <is>
+          <t>메시지를 보낼 때 그 장소에 있어 받은 플레이어 기록 테이블</t>
+        </is>
+      </c>
+      <c r="C2" s="47" t="n"/>
+      <c r="D2" s="47" t="n"/>
+      <c r="E2" s="47" t="n"/>
+      <c r="F2" s="47" t="n"/>
+      <c r="G2" s="47" t="n"/>
+      <c r="H2" s="48" t="n"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="38">
+      <c r="A4" s="41" t="inlineStr">
+        <is>
+          <t>순번</t>
+        </is>
+      </c>
+      <c r="B4" s="41" t="inlineStr">
+        <is>
+          <t>컬럼명</t>
+        </is>
+      </c>
+      <c r="C4" s="41" t="inlineStr">
+        <is>
+          <t>컬럼 설명</t>
+        </is>
+      </c>
+      <c r="D4" s="41" t="inlineStr">
+        <is>
+          <t>데이터타입</t>
+        </is>
+      </c>
+      <c r="E4" s="41" t="inlineStr">
+        <is>
+          <t>Null허용</t>
+        </is>
+      </c>
+      <c r="F4" s="41" t="inlineStr">
+        <is>
+          <t>기본값</t>
+        </is>
+      </c>
+      <c r="G4" s="41" t="inlineStr">
+        <is>
+          <t>특징</t>
+        </is>
+      </c>
+      <c r="H4" s="41" t="inlineStr">
+        <is>
+          <t>제약조건</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="38">
+      <c r="A5" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="50" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>대화수신 식별 번호</t>
+        </is>
+      </c>
+      <c r="D5" s="64" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E5" s="64" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F5" s="64" t="inlineStr">
+        <is>
+          <t>자동생성</t>
+        </is>
+      </c>
+      <c r="G5" s="64" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="H5" s="64" t="inlineStr">
+        <is>
+          <t>기본키(PK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="38">
+      <c r="A6" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="50" t="inlineStr">
+        <is>
+          <t>대화_번호</t>
+        </is>
+      </c>
+      <c r="C6" s="55" t="inlineStr">
+        <is>
+          <t>메시지 식별 번호</t>
+        </is>
+      </c>
+      <c r="D6" s="64" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E6" s="64" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F6" s="64" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G6" s="64" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H6" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">외래키(FK), 복합 UNIQUE(대화_번호, 계정_번호) </t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="38">
+      <c r="A7" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="50" t="inlineStr">
+        <is>
+          <t>계정_번호</t>
+        </is>
+      </c>
+      <c r="C7" s="55" t="inlineStr">
+        <is>
+          <t>메시지를 받은 계정 식별 번호</t>
+        </is>
+      </c>
+      <c r="D7" s="64" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E7" s="64" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F7" s="64" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G7" s="64" t="inlineStr">
+        <is>
+          <t>메시지를 보낼 때 같은 장소에 있던 플레이어(보낸 사람 포함)</t>
+        </is>
+      </c>
+      <c r="H7" s="64" t="inlineStr">
+        <is>
+          <t>외래키(FK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="38">
+      <c r="A8" s="42" t="n"/>
+      <c r="B8" s="50" t="n"/>
+      <c r="C8" s="55" t="n"/>
+      <c r="D8" s="64" t="n"/>
+      <c r="E8" s="64" t="n"/>
+      <c r="F8" s="64" t="n"/>
+      <c r="G8" s="64" t="n"/>
+      <c r="H8" s="64" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="38">
+      <c r="A9" s="42" t="n"/>
+      <c r="B9" s="50" t="n"/>
+      <c r="C9" s="55" t="n"/>
+      <c r="D9" s="64" t="n"/>
+      <c r="E9" s="55" t="n"/>
+      <c r="F9" s="55" t="n"/>
+      <c r="G9" s="55" t="n"/>
+      <c r="H9" s="55" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="38">
+      <c r="A10" s="42" t="n"/>
+      <c r="B10" s="50" t="n"/>
+      <c r="C10" s="55" t="n"/>
+      <c r="D10" s="55" t="n"/>
+      <c r="E10" s="55" t="n"/>
+      <c r="F10" s="55" t="n"/>
+      <c r="G10" s="55" t="n"/>
+      <c r="H10" s="55" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="38">
+      <c r="A11" s="42" t="n"/>
+      <c r="B11" s="50" t="n"/>
+      <c r="C11" s="55" t="n"/>
+      <c r="D11" s="72" t="n"/>
+      <c r="E11" s="55" t="n"/>
+      <c r="F11" s="55" t="n"/>
+      <c r="G11" s="55" t="n"/>
+      <c r="H11" s="55" t="n"/>
+    </row>
+    <row r="12" ht="16.5" customHeight="1" s="38">
+      <c r="A12" s="56" t="n"/>
+      <c r="B12" s="56" t="n"/>
+      <c r="C12" s="56" t="n"/>
+      <c r="D12" s="56" t="n"/>
+      <c r="E12" s="56" t="n"/>
+      <c r="F12" s="56" t="n"/>
+      <c r="G12" s="56" t="n"/>
+      <c r="H12" s="56" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1" location="'목차'!A1" r:id="rId1"/>
+  </hyperlinks>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -11816,7 +12512,6 @@
       <c r="G2" s="47" t="n"/>
       <c r="H2" s="48" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4" ht="16.5" customHeight="1" s="38">
       <c r="A4" s="41" t="inlineStr">
         <is>

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D12" s="44" t="n"/>
     </row>
@@ -14418,7 +14418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.62109375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="56" min="1" max="1"/>
@@ -14882,6 +14882,78 @@
       </c>
       <c r="H14" s="63" t="n"/>
     </row>
+    <row r="15">
+      <c r="A15" s="42" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="59" t="inlineStr">
+        <is>
+          <t>인물_순서</t>
+        </is>
+      </c>
+      <c r="C15" s="60" t="inlineStr">
+        <is>
+          <t>관련 인물 식별(캐릭터 이미지)</t>
+        </is>
+      </c>
+      <c r="D15" s="60" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E15" s="60" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F15" s="60" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G15" s="60" t="n"/>
+      <c r="H15" s="63" t="inlineStr">
+        <is>
+          <t>복합 외래키(작품_번호, 인물_순서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="59" t="inlineStr">
+        <is>
+          <t>공통스토리</t>
+        </is>
+      </c>
+      <c r="C16" s="60" t="inlineStr">
+        <is>
+          <t>작품의 공통 스토리에 붙는 미디어(영상) 여부</t>
+        </is>
+      </c>
+      <c r="D16" s="60" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="E16" s="60" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F16" s="60" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G16" s="60" t="n"/>
+      <c r="H16" s="63" t="inlineStr">
+        <is>
+          <t>CHECK (연결 대상이 정확히 하나: 단서·증언·조합·진행순서·인물 중 하나 또는 공통스토리)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:H1"/>

--- a/db/spec/schema_spec.xlsx
+++ b/db/spec/schema_spec.xlsx
@@ -758,6 +758,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16.5" customHeight="1" s="38">
       <c r="A4" s="41" t="inlineStr">
         <is>
@@ -888,7 +889,7 @@
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" s="44" t="n"/>
     </row>
@@ -14418,7 +14419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.62109375" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="56" min="1" max="1"/>
@@ -14472,6 +14473,7 @@
       <c r="G2" s="47" t="n"/>
       <c r="H2" s="48" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="16.5" customHeight="1" s="38">
       <c r="A4" s="41" t="inlineStr">
         <is>
@@ -14950,7 +14952,43 @@
       <c r="G16" s="60" t="n"/>
       <c r="H16" s="63" t="inlineStr">
         <is>
-          <t>CHECK (연결 대상이 정확히 하나: 단서·증언·조합·진행순서·인물 중 하나 또는 공통스토리)</t>
+          <t>CHECK (연결 대상이 정확히 하나: 단서·증언·조합·진행순서·인물 중 하나, 공통스토리 또는 표지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="59" t="inlineStr">
+        <is>
+          <t>표지</t>
+        </is>
+      </c>
+      <c r="C17" s="60" t="inlineStr">
+        <is>
+          <t>작품의 표지 이미지 여부(작품 목록·플레이 기록에 보임)</t>
+        </is>
+      </c>
+      <c r="D17" s="60" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="E17" s="60" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F17" s="60" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G17" s="60" t="n"/>
+      <c r="H17" s="63" t="inlineStr">
+        <is>
+          <t>연결 대상 CHECK 에 포함(위 공통스토리 설명 참고)</t>
         </is>
       </c>
     </row>
